--- a/data/trans_orig/IP3107-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3107-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53683</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49200</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62033</t>
+          <t>61908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>124887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>76412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65879</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>90471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123587</t>
+          <t>125617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159043</t>
+          <t>157999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33956</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>63341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>36839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238040</t>
+          <t>238030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266205</t>
+          <t>266132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265957</t>
+          <t>264154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296546</t>
+          <t>294034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511491</t>
+          <t>513328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554249</t>
+          <t>553076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>21087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116712</t>
+          <t>116638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89235</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104386</t>
+          <t>103731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193985</t>
+          <t>193309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216425</t>
+          <t>215525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>79134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87846</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117876</t>
+          <t>117656</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176300</t>
+          <t>176593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216450</t>
+          <t>215727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32772</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>65395</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>91731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51427</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>403712</t>
+          <t>403989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>438196</t>
+          <t>440301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>414833</t>
+          <t>414901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>451740</t>
+          <t>450754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>830515</t>
+          <t>829497</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>879277</t>
+          <t>878716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54672</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>67537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98845</t>
+          <t>99755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118470</t>
+          <t>119734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>51261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76132</t>
+          <t>77101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>22089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,82 +4501,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20136</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>28214</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>20479</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>37667</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12830</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7859</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19911</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>28214</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>38075</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>49252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73577</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37821</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>38409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>60104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275434</t>
+          <t>276806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302096</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285452</t>
+          <t>285576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315578</t>
+          <t>316216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571402</t>
+          <t>567563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610513</t>
+          <t>609699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99811</t>
+          <t>99896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115782</t>
+          <t>115555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104396</t>
+          <t>104976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>120244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209920</t>
+          <t>209351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231920</t>
+          <t>232856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57548</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41069</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>62353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114473</t>
+          <t>113984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>27889</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,82 +5978,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>61246</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>49771</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>74722</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>100539</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>86069</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>118124</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>61246</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>48738</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>75107</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>100539</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>85562</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>116050</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53215</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79522</t>
+          <t>79326</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>443985</t>
+          <t>443536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>477341</t>
+          <t>476741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>442780</t>
+          <t>441587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>479750</t>
+          <t>480487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>898105</t>
+          <t>896099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>946836</t>
+          <t>945788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39489</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49315</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43400</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86446</t>
+          <t>86236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100947</t>
+          <t>101423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>50701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>49491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35534</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>55046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>80311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332876</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358710</t>
+          <t>358883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355380</t>
+          <t>357287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382152</t>
+          <t>383463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696417</t>
+          <t>698490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734243</t>
+          <t>735480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,47 +8368,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7555</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>7555</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>13210</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118139</t>
+          <t>118273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132996</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127833</t>
+          <t>127451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143564</t>
+          <t>143243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251828</t>
+          <t>251789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>271988</t>
+          <t>272010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>86789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>71106</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52594</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77207</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>107081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>501461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>533015</t>
+          <t>532190</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>537648</t>
+          <t>538165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>571964</t>
+          <t>571222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1048934</t>
+          <t>1045306</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1094573</t>
+          <t>1092909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
